--- a/Hoàng/2025/T6/CUNG THIẾU NHI (102-2025) (TB 64-2025)/DS, DM CUNG THIẾU NHI.xlsx
+++ b/Hoàng/2025/T6/CUNG THIẾU NHI (102-2025) (TB 64-2025)/DS, DM CUNG THIẾU NHI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\DATA-TN\Hoàng\2025\T6\CUNG THIẾU NHI (102-2025) (TB 64-2025)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D79F0C75-C2A8-4BFD-B3CD-021E180BF287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C724788E-82BD-44D2-B32E-CBD109262347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DS" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="113">
   <si>
     <t>HỌ TÊN</t>
   </si>
@@ -332,13 +332,55 @@
   </si>
   <si>
     <t>Khám da liễu</t>
+  </si>
+  <si>
+    <t>MÃ NV</t>
+  </si>
+  <si>
+    <t>NV01</t>
+  </si>
+  <si>
+    <t>NV02</t>
+  </si>
+  <si>
+    <t>NV03</t>
+  </si>
+  <si>
+    <t>NV04</t>
+  </si>
+  <si>
+    <t>NV05</t>
+  </si>
+  <si>
+    <t>NV06</t>
+  </si>
+  <si>
+    <t>NV07</t>
+  </si>
+  <si>
+    <t>NV08</t>
+  </si>
+  <si>
+    <t>NV09</t>
+  </si>
+  <si>
+    <t>NV10</t>
+  </si>
+  <si>
+    <t>NV11</t>
+  </si>
+  <si>
+    <t>NV12</t>
+  </si>
+  <si>
+    <t>NV13</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -382,6 +424,12 @@
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="10">
@@ -834,295 +882,339 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="1">
+      <c r="F2" s="1">
         <v>1984</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="1">
+      <c r="F3" s="1">
         <v>1981</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="1">
+      <c r="F4" s="1">
         <v>1992</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="1">
+      <c r="F5" s="1">
         <v>1989</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="1">
+      <c r="F6" s="1">
         <v>1991</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="1">
+      <c r="F7" s="1">
         <v>1976</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="1">
+      <c r="F8" s="1">
         <v>1985</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="1">
+      <c r="F9" s="1">
         <v>1990</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="G9" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="1">
+      <c r="F10" s="1">
         <v>1986</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="D11" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="1">
+      <c r="F11" s="1">
         <v>1995</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="G11" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="1">
+      <c r="F12" s="1">
         <v>1969</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="G12" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="1">
+      <c r="F13" s="1">
         <v>1971</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="G13" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="3"/>
+      <c r="E14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="1">
+      <c r="F14" s="1">
         <v>1987</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="G14" s="4" t="s">
         <v>36</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Hoàng/2025/T6/CUNG THIẾU NHI (102-2025) (TB 64-2025)/DS, DM CUNG THIẾU NHI.xlsx
+++ b/Hoàng/2025/T6/CUNG THIẾU NHI (102-2025) (TB 64-2025)/DS, DM CUNG THIẾU NHI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\DATA-TN\Hoàng\2025\T6\CUNG THIẾU NHI (102-2025) (TB 64-2025)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C724788E-82BD-44D2-B32E-CBD109262347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD8454FA-EF4C-4BF3-A9C2-1C4AF173E3D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DS" sheetId="1" r:id="rId1"/>
@@ -882,11 +882,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.28515625" hidden="1" customWidth="1"/>
     <col min="3" max="3" width="26.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="12.140625" bestFit="1" customWidth="1"/>
@@ -1216,6 +1219,7 @@
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Hoàng/2025/T6/CUNG THIẾU NHI (102-2025) (TB 64-2025)/DS, DM CUNG THIẾU NHI.xlsx
+++ b/Hoàng/2025/T6/CUNG THIẾU NHI (102-2025) (TB 64-2025)/DS, DM CUNG THIẾU NHI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\DATA-TN\Hoàng\2025\T6\CUNG THIẾU NHI (102-2025) (TB 64-2025)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD8454FA-EF4C-4BF3-A9C2-1C4AF173E3D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A53A7C3-9B7E-4A20-A32A-59F2D04C7F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="DS" sheetId="1" r:id="rId1"/>
     <sheet name="DM" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">DS!$A$1:$G$15</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -35,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="115">
   <si>
     <t>HỌ TÊN</t>
   </si>
@@ -374,6 +377,12 @@
   </si>
   <si>
     <t>NV13</t>
+  </si>
+  <si>
+    <t>Huỳnh Thị Lệ Thu</t>
+  </si>
+  <si>
+    <t>NV14</t>
   </si>
 </sst>
 </file>
@@ -488,7 +497,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -539,11 +548,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -600,6 +620,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -885,11 +908,11 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.28515625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="8.28515625" customWidth="1"/>
     <col min="3" max="3" width="26.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="12.140625" bestFit="1" customWidth="1"/>
@@ -1216,10 +1239,27 @@
         <v>36</v>
       </c>
     </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="20">
+        <v>14</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="C15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" s="20">
+        <v>1978</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="93" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
